--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_nuble.xlsx
@@ -471,7 +471,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:32</t>
+    <t xml:space="preserve">2026-09-18 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2024_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">362</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">120</t>
@@ -471,7 +471,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:12</t>
+    <t xml:space="preserve">2026-10-05 04:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
